--- a/Assets/Excel/MapLock_5 .xlsx
+++ b/Assets/Excel/MapLock_5 .xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17865" windowHeight="10845"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1045,7 +1045,7 @@
         <v>2</v>
       </c>
       <c r="B5">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C5">
         <v>32000</v>
